--- a/vse-loti/341356380/spec-341356380.xlsx
+++ b/vse-loti/341356380/spec-341356380.xlsx
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +96,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -464,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1384,7 +1387,7 @@
         </is>
       </c>
       <c r="G37" s="8" t="n">
-        <v>3113302.46</v>
+        <v>3113303.22</v>
       </c>
     </row>
     <row r="38">
@@ -1394,22 +1397,29 @@
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>3798229</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+        <v>3798229.93</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>НДС 22 %, ставка из документа: "евяносто восемь тысяч двести двадцать девять рублей 93 копейки) в т.ч НДС 22%." — TZ novaya .txt; суммы источника указаны с НДС: "ьсот девяносто восемь тысяч двести двадцать девять рублей 93 копейки) в т.ч НДС 22%." — ТЗ новая .doc. «с НДС» — сумма из документа, «без НДС» = сумма ÷ 1,22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>Источник: НМЦК.xlsx
 ТЗ новая .doc</t>
         </is>
       </c>
     </row>
-    <row r="41"/>
     <row r="42"/>
+    <row r="43"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A40:B42"/>
+    <mergeCell ref="A41:B43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/341356380/spec-341356380.xlsx
+++ b/vse-loti/341356380/spec-341356380.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -479,6 +479,7 @@
     <col width="20.28515625" customWidth="1" min="7" max="7"/>
     <col width="18.85546875" customWidth="1" min="8" max="8"/>
     <col width="16.42578125" customWidth="1" min="9" max="9"/>
+    <col width="18.85546875" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -514,17 +515,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Цена за т (без НДС)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Стоимость (с НДС)</t>
         </is>
       </c>
     </row>
@@ -553,7 +559,7 @@
       <c r="F2" s="4" t="n">
         <v>0.439</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -575,7 +581,7 @@
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -601,7 +607,7 @@
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -627,7 +633,7 @@
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -649,7 +655,7 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -677,7 +683,7 @@
       <c r="F7" s="4" t="n">
         <v>10.08</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -705,7 +711,7 @@
       <c r="F8" s="4" t="n">
         <v>1.562</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -733,7 +739,7 @@
       <c r="F9" s="4" t="n">
         <v>0.895</v>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -761,7 +767,7 @@
       <c r="F10" s="4" t="n">
         <v>0.756</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -787,7 +793,7 @@
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -813,7 +819,7 @@
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -839,7 +845,7 @@
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -865,7 +871,7 @@
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -891,7 +897,7 @@
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -917,7 +923,7 @@
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -943,7 +949,7 @@
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -969,7 +975,7 @@
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -995,7 +1001,7 @@
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1021,7 +1027,7 @@
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1047,7 +1053,7 @@
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1073,7 +1079,7 @@
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1099,7 +1105,7 @@
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1125,7 +1131,7 @@
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1147,7 +1153,7 @@
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1169,7 +1175,7 @@
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1191,7 +1197,7 @@
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1213,7 +1219,7 @@
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1235,7 +1241,7 @@
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1257,7 +1263,7 @@
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1279,7 +1285,7 @@
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -1301,7 +1307,7 @@
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1323,7 +1329,7 @@
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
@@ -1345,7 +1351,7 @@
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -1367,7 +1373,7 @@
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -1386,7 +1392,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G37" s="8" t="n">
+      <c r="H37" s="8" t="n">
         <v>3113303.22</v>
       </c>
     </row>
@@ -1396,7 +1402,7 @@
           <t>НМЦК с НДС 22%:</t>
         </is>
       </c>
-      <c r="F38" s="8" t="n">
+      <c r="J38" s="8" t="n">
         <v>3798229.93</v>
       </c>
     </row>

--- a/vse-loti/341356380/spec-341356380.xlsx
+++ b/vse-loti/341356380/spec-341356380.xlsx
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +96,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -467,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -564,278 +567,228 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Комплект изоляции стыкового соединения</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" s="3" t="n">
-        <v>8</v>
+          <t>Труба стальная электросварная прямошовная Ст.219х7,0/315-ППУ1-ОЦ</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>219×7</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>275.4</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>10.08</v>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Отвод ст.УК 219х7-900-ППУ-ОЦ (700х700)</t>
+          <t>Труба стальная электросварная прямошовная Ст.159х6,0/250-ППУ1-ОЦ</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>219×7</t>
+          <t>159×6</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>1.562</v>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Отвод 219х7-900-ППУ-ОЦ (1000х1000)</t>
+          <t>Труба стальная электросварная прямошовная Ст.89х5,0/180-ППУ1-ОЦ</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>219×7</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>2</v>
+          <t>89×5</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>86.40000000000001</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0.895</v>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Скользящая опора</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" s="3" t="n">
-        <v>4</v>
+          <t>Труба стальная электросварная прямошовная Ст.76х5,0/160-ППУ1-ОЦ</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>76×5</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>86.40000000000001</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0.756</v>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Труба стальная электросварная прямошовная Ст.219х7,0/315-ППУ1-ОЦ</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>219×7</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>275.4</v>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Прочие позиции лота (29) — не трубы, в трубную часть и в цену за тонну не входят</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная Ст.159х6,0/250-ППУ1-ОЦ</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>159×6</t>
-        </is>
-      </c>
+          <t>Комплект изоляции стыкового соединения</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="3" t="n">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>1.562</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+          <t>шт</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная Ст.89х5,0/180-ППУ1-ОЦ</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>89×5</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>86.40000000000001</v>
+          <t>Отвод ст.УК 219х7-900-ППУ-ОЦ (700х700)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>шт</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная Ст.76х5,0/160-ППУ1-ОЦ</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>76×5</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>86.40000000000001</v>
+          <t>Отвод 219х7-900-ППУ-ОЦ (1000х1000)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>0.756</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>шт</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Отвод ст. 219х7,0-900 ППУ-ОЦ</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>219×7</t>
-        </is>
-      </c>
+          <t>Скользящая опора</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="3" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Отвод* ст. 219х7,0-720 ППУ-ОЦ</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>219×7</t>
-        </is>
-      </c>
+          <t>Отвод ст. 219х7,0-900 ППУ-ОЦ</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="3" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Отвод ст. 219х7,0-220 ППУ-ОЦ</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>219×7</t>
-        </is>
-      </c>
+          <t>Отвод* ст. 219х7,0-720 ППУ-ОЦ</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="3" t="n">
         <v>2</v>
       </c>
@@ -844,102 +797,74 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Отвод ст. 159х6,0-900 ППУ-ОЦ</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>159×6</t>
-        </is>
-      </c>
+          <t>Отвод ст. 219х7,0-220 ППУ-ОЦ</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Отвод ст. 89х5,0-900 ППУ-ОЦ (1000х1000мм)</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>89×5</t>
-        </is>
-      </c>
+          <t>Отвод ст. 159х6,0-900 ППУ-ОЦ</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Отвод ст. 89х5,0-720 ППУ-ОЦ (1000х1000мм)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>89×5</t>
-        </is>
-      </c>
+          <t>Отвод ст. 89х5,0-900 ППУ-ОЦ (1000х1000мм)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Отвод ст. 89х5,0-220 ППУ-ОЦ (1000х1000мм)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>89×5</t>
-        </is>
-      </c>
+          <t>Отвод ст. 89х5,0-720 ППУ-ОЦ (1000х1000мм)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="3" t="n">
         <v>1</v>
       </c>
@@ -948,76 +873,55 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Отвод ст. 76х5,0-900 ППУ-ОЦ (1000х1000мм)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>76×5</t>
-        </is>
-      </c>
+          <t>Отвод ст. 89х5,0-220 ППУ-ОЦ (1000х1000мм)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Отвод ст. 76х5,0-720 ППУ-ОЦ (1000х1000мм)</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>76×5</t>
-        </is>
-      </c>
+          <t>Отвод ст. 76х5,0-900 ППУ-ОЦ (1000х1000мм)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
       <c r="D19" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Отвод ст. 76х5,0-220 ППУ-ОЦ (1000х1000мм)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>76×5</t>
-        </is>
-      </c>
+          <t>Отвод ст. 76х5,0-720 ППУ-ОЦ (1000х1000мм)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="3" t="n">
         <v>1</v>
       </c>
@@ -1026,24 +930,17 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Переход ст. 273х7,0-219х7.0 ППУ-ОЦ 400/315</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>273×7</t>
-        </is>
-      </c>
+          <t>Отвод ст. 76х5,0-220 ППУ-ОЦ (1000х1000мм)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="3" t="n">
         <v>1</v>
       </c>
@@ -1052,24 +949,17 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Переход ст. 219х7,0-159х6,0ППУ-ОЦ 315/250</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>219×7</t>
-        </is>
-      </c>
+          <t>Переход ст. 273х7,0-219х7.0 ППУ-ОЦ 400/315</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="3" t="n">
         <v>1</v>
       </c>
@@ -1078,24 +968,17 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Переход ст. 219х7,0-89х5,0 ППУ-ОЦ</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>219×7</t>
-        </is>
-      </c>
+          <t>Переход ст. 219х7,0-159х6,0ППУ-ОЦ 315/250</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="3" t="n">
         <v>1</v>
       </c>
@@ -1104,24 +987,17 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Переход ст. 159х6,0-76х5,0 ППУ-ОЦ</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>159×6</t>
-        </is>
-      </c>
+          <t>Переход ст. 219х7,0-89х5,0 ППУ-ОЦ</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="3" t="n">
         <v>1</v>
       </c>
@@ -1130,86 +1006,74 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Комплект изоляции стыкового соединения</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>Переход ст. 159х6,0-76х5,0 ППУ-ОЦ</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
       <c r="D25" s="3" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Комплект изоляции стыкового соединения</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="3" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Комплект изоляции стыкового соединения</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Комплект изоляции стыкового соединения</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="3" t="n">
         <v>12</v>
       </c>
@@ -1218,64 +1082,55 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Заглушка изоляции ОЦ</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>Комплект изоляции стыкового соединения</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Заглушка изоляции ОЦ</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Заглушка изоляции ОЦ</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="3" t="n">
         <v>1</v>
       </c>
@@ -1284,86 +1139,74 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Скользящая опора</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>Заглушка изоляции ОЦ</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="3" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Скользящая опора</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="3" t="n">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Скользящая опора</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Скользящая опора</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="3" t="n">
         <v>16</v>
       </c>
@@ -1372,60 +1215,84 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>13.732</v>
+      <c r="A36" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Скользящая опора</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>НМЦК из обоснования:</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="n">
-        <v>3113303.22</v>
+          <t>ИТОГО трубная часть</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>13.732</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
+          <t>НМЦК из обоснования:</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>3113303.22</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
           <t>НМЦК с НДС 22%:</t>
         </is>
       </c>
-      <c r="J38" s="8" t="n">
+      <c r="J39" s="8" t="n">
         <v>3798229.93</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>НДС 22 %, ставка из документа: "евяносто восемь тысяч двести двадцать девять рублей 93 копейки) в т.ч НДС 22%." — TZ novaya .txt; суммы источника указаны с НДС: "ьсот девяносто восемь тысяч двести двадцать девять рублей 93 копейки) в т.ч НДС 22%." — ТЗ новая .doc. «с НДС» — сумма из документа, «без НДС» = сумма ÷ 1,22.</t>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>Трубная часть лота: 5 из 34 позиций; остальное — не трубы (комплект, отвод, скользящая, отвод*, переход, заглушка, …) — показано ниже отдельным блоком, без массы и цены за тонну. «ИТОГО трубная часть» — только трубы, «ВСЕГО по лоту» — все позиции.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
+          <t>НДС 22 %, ставка из документа: "евяносто восемь тысяч двести двадцать девять рублей 93 копейки) в т.ч НДС 22%." — TZ novaya .txt; суммы источника указаны с НДС: "ьсот девяносто восемь тысяч двести двадцать девять рублей 93 копейки) в т.ч НДС 22%." — ТЗ новая .doc. «с НДС» — сумма из документа, «без НДС» = сумма ÷ 1,22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
           <t>Источник: НМЦК.xlsx
 ТЗ новая .doc</t>
         </is>
       </c>
     </row>
-    <row r="42"/>
-    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A41:B43"/>
+  <mergeCells count="2">
+    <mergeCell ref="A43:B45"/>
+    <mergeCell ref="A7:J7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
